--- a/utils/monday_sprint_sprint_2025-23.xlsx
+++ b/utils/monday_sprint_sprint_2025-23.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="242">
   <si>
     <t>Ticket</t>
   </si>
@@ -246,6 +246,9 @@
     <t>Robmar Xavier</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>34375</t>
   </si>
   <si>
@@ -309,7 +312,7 @@
     <t>26/03/2024</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -459,7 +462,7 @@
     <t>23/10/2025</t>
   </si>
   <si>
-    <t>15/03/2026</t>
+    <t>10/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -600,7 +603,7 @@
     <t>08/08/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Agosto</t>
@@ -2168,7 +2171,7 @@
         <v>38</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>55</v>
@@ -2182,7 +2185,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2194,10 +2197,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>27</v>
@@ -2238,10 +2241,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2282,10 +2285,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2314,7 +2317,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2326,10 +2329,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2350,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
@@ -2358,7 +2361,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2370,25 +2373,25 @@
         <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>20</v>
@@ -2397,12 +2400,12 @@
         <v>21</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2414,10 +2417,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2438,7 +2441,7 @@
         <v>20</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>17</v>
@@ -2446,7 +2449,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2458,39 +2461,39 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2502,10 +2505,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2526,7 +2529,7 @@
         <v>20</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>17</v>
@@ -2534,7 +2537,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2546,10 +2549,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>27</v>
@@ -2570,7 +2573,7 @@
         <v>20</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>17</v>
@@ -2578,7 +2581,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2590,10 +2593,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2614,7 +2617,7 @@
         <v>20</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>17</v>
@@ -2622,7 +2625,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2634,39 +2637,39 @@
         <v>33</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2678,10 +2681,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>27</v>
@@ -2702,7 +2705,7 @@
         <v>55</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>17</v>
@@ -2710,7 +2713,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2722,10 +2725,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2746,7 +2749,7 @@
         <v>55</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>17</v>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2766,10 +2769,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>27</v>
@@ -2790,7 +2793,7 @@
         <v>20</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>17</v>
@@ -2810,10 +2813,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2834,7 +2837,7 @@
         <v>20</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>17</v>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2854,10 +2857,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2878,7 +2881,7 @@
         <v>20</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>17</v>
@@ -2886,7 +2889,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2898,10 +2901,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -2922,7 +2925,7 @@
         <v>20</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>17</v>
@@ -2930,7 +2933,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2942,10 +2945,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -2966,7 +2969,7 @@
         <v>20</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>17</v>
@@ -2974,7 +2977,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2986,10 +2989,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3010,7 +3013,7 @@
         <v>20</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>17</v>
@@ -3018,7 +3021,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3030,10 +3033,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -3054,7 +3057,7 @@
         <v>20</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>17</v>
@@ -3062,7 +3065,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3074,10 +3077,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3142,7 +3145,7 @@
         <v>24</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>17</v>
@@ -3150,7 +3153,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3162,10 +3165,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3186,7 +3189,7 @@
         <v>20</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>17</v>
@@ -3194,7 +3197,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3206,10 +3209,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3238,7 +3241,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3250,10 +3253,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3274,7 +3277,7 @@
         <v>20</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>17</v>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3294,10 +3297,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3318,7 +3321,7 @@
         <v>20</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>17</v>
@@ -3326,7 +3329,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3338,10 +3341,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3362,7 +3365,7 @@
         <v>20</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>17</v>
@@ -3370,7 +3373,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3382,10 +3385,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3406,7 +3409,7 @@
         <v>42</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>17</v>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3426,39 +3429,39 @@
         <v>33</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3470,22 +3473,22 @@
         <v>33</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>17</v>
@@ -3494,15 +3497,15 @@
         <v>20</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3514,22 +3517,22 @@
         <v>33</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>17</v>
@@ -3538,15 +3541,15 @@
         <v>45</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3558,10 +3561,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>27</v>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3602,10 +3605,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3626,7 +3629,7 @@
         <v>42</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>17</v>
@@ -3634,7 +3637,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3646,13 +3649,13 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>17</v>
@@ -3678,7 +3681,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3690,10 +3693,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3722,7 +3725,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3734,10 +3737,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3766,7 +3769,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3778,10 +3781,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3802,7 +3805,7 @@
         <v>20</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>17</v>
@@ -3810,7 +3813,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3822,10 +3825,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>27</v>
@@ -3854,7 +3857,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3866,22 +3869,22 @@
         <v>33</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>17</v>
@@ -3890,7 +3893,7 @@
         <v>20</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>39</v>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3910,10 +3913,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3934,7 +3937,7 @@
         <v>20</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>17</v>
@@ -3942,7 +3945,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3954,10 +3957,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -3978,7 +3981,7 @@
         <v>45</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>17</v>
@@ -3986,7 +3989,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -3998,13 +4001,13 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>17</v>
@@ -4030,7 +4033,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4042,10 +4045,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4066,7 +4069,7 @@
         <v>20</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>17</v>
@@ -4074,7 +4077,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4086,13 +4089,13 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>17</v>
@@ -4118,7 +4121,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4130,10 +4133,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4174,25 +4177,25 @@
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>37</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>42</v>
@@ -4201,12 +4204,12 @@
         <v>62</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4218,10 +4221,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4242,7 +4245,7 @@
         <v>20</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>17</v>
@@ -4250,7 +4253,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4262,10 +4265,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>27</v>
@@ -4286,7 +4289,7 @@
         <v>55</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>17</v>
@@ -4294,7 +4297,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4306,10 +4309,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>27</v>
@@ -4330,7 +4333,7 @@
         <v>55</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>17</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4350,10 +4353,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>27</v>
@@ -4382,7 +4385,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4394,10 +4397,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4426,7 +4429,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4438,22 +4441,22 @@
         <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>17</v>
@@ -4465,12 +4468,12 @@
         <v>62</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4482,10 +4485,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4506,7 +4509,7 @@
         <v>20</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>17</v>
@@ -4525,23 +4528,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4549,16 +4552,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4577,7 +4580,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4598,7 +4601,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4629,12 +4632,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -4658,25 +4661,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4693,13 +4696,13 @@
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4714,7 +4717,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -4731,7 +4734,7 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K11">
         <v>75</v>
@@ -4746,7 +4749,7 @@
         <v>62</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -4769,35 +4772,35 @@
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4809,10 +4812,10 @@
         <v>7</v>
       </c>
       <c r="P14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q14">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -4825,7 +4828,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4833,7 +4836,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4841,7 +4844,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -4852,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4860,35 +4863,35 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -4897,40 +4900,40 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
@@ -4939,21 +4942,21 @@
         <v>332</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4964,7 +4967,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -4978,7 +4981,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>74</v>
@@ -4986,16 +4989,16 @@
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-23.xlsx
+++ b/utils/monday_sprint_sprint_2025-23.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="249">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>34533</t>
+    <t>18330965955</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>03/11/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>16/11/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,19 +102,19 @@
     <t>Novembro</t>
   </si>
   <si>
-    <t>34171</t>
+    <t>18330603251</t>
   </si>
   <si>
     <t>Contagem Proformas</t>
   </si>
   <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>33772</t>
+    <t>18330966812</t>
   </si>
   <si>
     <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
@@ -123,18 +123,24 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>34109</t>
+    <t>02/11/2025</t>
+  </si>
+  <si>
+    <t>18331221944</t>
   </si>
   <si>
     <t>Melhorias Sistema Manutenção - Apresentação</t>
   </si>
   <si>
-    <t>34693</t>
+    <t>18330967025</t>
   </si>
   <si>
     <t>Motivos de retrabalho da moldagem</t>
   </si>
   <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
     <t>33965</t>
   </si>
   <si>
@@ -156,31 +162,40 @@
     <t>Sistemas</t>
   </si>
   <si>
-    <t>34793</t>
+    <t>18331085113</t>
   </si>
   <si>
     <t>Chamado para revisão BI Manutenção - Chamado Principal</t>
   </si>
   <si>
+    <t>09/11/2025</t>
+  </si>
+  <si>
     <t>Homologação</t>
   </si>
   <si>
-    <t>34246</t>
+    <t>18331239298</t>
   </si>
   <si>
     <t>URGENTE - divergências refugo aplicação Relator x SENSE</t>
   </si>
   <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>33412</t>
+    <t>18331221982</t>
   </si>
   <si>
     <t>Atualização de Metas - Equipamento - Apresentação</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>18331172285</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -189,13 +204,19 @@
     <t>Ajustes Dalca e Lianco</t>
   </si>
   <si>
+    <t>18331085419</t>
+  </si>
+  <si>
     <t>Corrigir duplicidade de dados na base da aplicação</t>
   </si>
   <si>
+    <t>18331222048</t>
+  </si>
+  <si>
     <t>Atualização de Metas - Local - Apresentação</t>
   </si>
   <si>
-    <t>33588</t>
+    <t>18332293244</t>
   </si>
   <si>
     <t>Indicador Cobertura de Estoques</t>
@@ -204,7 +225,7 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>35004</t>
+    <t>18342098062</t>
   </si>
   <si>
     <t>Solicitação de ajustes no sistema de inventário WMS do almoxarifado</t>
@@ -213,10 +234,16 @@
     <t>04/11/2025</t>
   </si>
   <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>18331085488</t>
+  </si>
+  <si>
     <t>Campo calculado de % Disponibilidade / MTTR e MTBF</t>
   </si>
   <si>
-    <t>35222</t>
+    <t>18376310313</t>
   </si>
   <si>
     <t>Correção</t>
@@ -225,40 +252,34 @@
     <t>modelo 53926158</t>
   </si>
   <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>34432</t>
+    <t>18331171581</t>
   </si>
   <si>
     <t>Modificar Painel Manipuladores para APON3</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>18353206552</t>
   </si>
   <si>
     <t>Revisar o acesso as tabelas</t>
   </si>
   <si>
-    <t>05/11/2025</t>
-  </si>
-  <si>
-    <t>34894</t>
+    <t>18331171415</t>
   </si>
   <si>
     <t>Novos modelos para Apontamento Digital</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>18331172626</t>
   </si>
   <si>
     <t>Sessões de conversa assistente IA - Criar estrutura de Sessões</t>
   </si>
   <si>
-    <t>33933</t>
+    <t>18331221779</t>
   </si>
   <si>
     <t>Criar campo para gatilho de analise de causa raiz (Aguardar formulário)</t>
@@ -267,6 +288,9 @@
     <t>33956</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Definição de metas de custos de manutenção (META GERAL)</t>
   </si>
   <si>
@@ -279,19 +303,25 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>34375</t>
+    <t>18331222117</t>
   </si>
   <si>
     <t>Criação e novo responsável refugo</t>
   </si>
   <si>
+    <t>18332671013</t>
+  </si>
+  <si>
     <t>Sessões de conversa assistente IA - Criar API's</t>
   </si>
   <si>
+    <t>18332673324</t>
+  </si>
+  <si>
     <t>Sessões de conversa assistente IA - Ajustes no Front End</t>
   </si>
   <si>
-    <t>34973</t>
+    <t>18321184450</t>
   </si>
   <si>
     <t>Lock no lançamento de notas fiscais</t>
@@ -309,6 +339,9 @@
     <t>32150</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Inventario WMS - Registro de Ajuste de Box</t>
   </si>
   <si>
@@ -324,7 +357,7 @@
     <t>29/10/2025</t>
   </si>
   <si>
-    <t>34363</t>
+    <t>18221513926</t>
   </si>
   <si>
     <t>MODELO UNIVERSAL - Analise</t>
@@ -348,13 +381,13 @@
     <t>20/03/2026</t>
   </si>
   <si>
-    <t>34949</t>
+    <t>18321253863</t>
   </si>
   <si>
     <t>Incluir valor de SIC e OSI no cadastro de projetos</t>
   </si>
   <si>
-    <t>34596</t>
+    <t>18212487286</t>
   </si>
   <si>
     <t>Melhorias e correções na aplicação do refugo</t>
@@ -363,7 +396,7 @@
     <t>17/10/2025</t>
   </si>
   <si>
-    <t>35003</t>
+    <t>18321125802</t>
   </si>
   <si>
     <t>Verificar range das preventivas</t>
@@ -378,7 +411,7 @@
     <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
   </si>
   <si>
-    <t>33807</t>
+    <t>18236204631</t>
   </si>
   <si>
     <t>Interface para o usuário realizar a integração com OpCenter</t>
@@ -387,109 +420,106 @@
     <t>21/10/2025</t>
   </si>
   <si>
-    <t>34534</t>
+    <t>18212589655</t>
   </si>
   <si>
     <t>Indicadores de Setup - IROG Usinagem</t>
   </si>
   <si>
-    <t>34974</t>
+    <t>18321170650</t>
   </si>
   <si>
     <t>Projeto BI IROG SPA - Criar tela de cadastro de metas para BI</t>
   </si>
   <si>
+    <t>18321404241</t>
+  </si>
+  <si>
     <t>Cadastramento dos ENGs para Mapeamento Digital</t>
   </si>
   <si>
-    <t>34887</t>
+    <t>18321466579</t>
   </si>
   <si>
     <t>Altona || UEXP_IMO - Estoque de IMOB - Exportação</t>
   </si>
   <si>
-    <t>34613</t>
+    <t>18321823153</t>
   </si>
   <si>
     <t>ADICIONAR - OPERAÇÃO | DESCRIÇÃO DA OPERAÇÃO - ESMERIL DE PÇ BRUTA SEM JATO / ESCARFAGEM DE PEÇA BRUTA SEM JATO. NO SISTEMA DE APONTAMENTO ELETRONICO ACABAMENTO!</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>18301762137</t>
   </si>
   <si>
     <t>Ordem de coleta - controle de pátio</t>
   </si>
   <si>
-    <t>34885</t>
+    <t>18321588372</t>
   </si>
   <si>
     <t>PARADAS JATOS</t>
   </si>
   <si>
-    <t>34886</t>
+    <t>18321478574</t>
   </si>
   <si>
     <t>Sistema Importação - Ajustes</t>
   </si>
   <si>
-    <t>34027</t>
+    <t>18330588363</t>
   </si>
   <si>
     <t>LOG TRANSFERENCIA NO SISTEMA INVOICE - AJUSTE SISTEMA GESTÃO A VISTA</t>
   </si>
   <si>
-    <t>34878</t>
+    <t>18321771371</t>
+  </si>
+  <si>
+    <t>18321605687</t>
   </si>
   <si>
     <t>Digitação de volume livre - Totalizador de impostos</t>
   </si>
   <si>
-    <t>34076</t>
+    <t>18330597917</t>
   </si>
   <si>
     <t>Sistema de registro</t>
   </si>
   <si>
-    <t>34868</t>
+    <t>18321617745</t>
   </si>
   <si>
     <t>Melhoria SISTEMA CORTE PÓ DE FERRO</t>
   </si>
   <si>
-    <t>34583</t>
+    <t>18321983721</t>
   </si>
   <si>
     <t>dados cartão ponto X apontamento</t>
   </si>
   <si>
-    <t>34597</t>
+    <t>18321959287</t>
   </si>
   <si>
     <t>Melhoria | Inclusão do Campo de hora de Saida</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>18236205464</t>
   </si>
   <si>
     <t>B.I ordens de manutenção maquinas pneumáticas</t>
   </si>
   <si>
-    <t>34860</t>
+    <t>18321805301</t>
   </si>
   <si>
     <t>Sistema de Lotes</t>
   </si>
   <si>
-    <t>Bom dia, Precisamos que seja feita uma alteração no sistema de lotes da aciaria Hoje precisamos digitar para cada forno 1 lote, tornando uma tarefa repetitiva, Precisamos que seja colocado 3 colunas apenas que serão elas: INDUÇÃO -&gt; FORNO 8, FORNO 10 e 6. ARCO -&gt; FORNO 4 AOD -&gt; FORNO 9 FORNO 3 e FOR</t>
-  </si>
-  <si>
-    <t>Maycon Douglas Alesio Cecilio</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>31836</t>
+    <t>18302093353</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
@@ -504,19 +534,19 @@
     <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
   </si>
   <si>
-    <t>34605</t>
+    <t>18330627834</t>
   </si>
   <si>
     <t>Dificuldade em deixar registros em sequências que ficam paradas em fusão</t>
   </si>
   <si>
-    <t>34595</t>
+    <t>18321972783</t>
   </si>
   <si>
     <t>PID Rejeitando cotas Aprovadas</t>
   </si>
   <si>
-    <t>34721</t>
+    <t>18330871692</t>
   </si>
   <si>
     <t>Solicitação de melhoria no WMS – Retenção de dados na pré-lista</t>
@@ -525,25 +555,25 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>34652</t>
+    <t>18330640841</t>
   </si>
   <si>
     <t>Atualização retroativa (desde jan/2024)</t>
   </si>
   <si>
-    <t>33394</t>
+    <t>18330611255</t>
   </si>
   <si>
     <t>Documentos do sistema Invoice – saindo cortados</t>
   </si>
   <si>
-    <t>34577</t>
+    <t>18321994683</t>
   </si>
   <si>
     <t>Coluna Planilhão</t>
   </si>
   <si>
-    <t>32588</t>
+    <t>18330871413</t>
   </si>
   <si>
     <t>Baixa de Estoque de Embalagem Expedição - Gerar requisição</t>
@@ -564,75 +594,75 @@
     <t>Willian Gabriel Paixão dos Santos</t>
   </si>
   <si>
-    <t>31794</t>
+    <t>18302001816</t>
   </si>
   <si>
     <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
   </si>
   <si>
-    <t>34942</t>
+    <t>18321306739</t>
   </si>
   <si>
     <t>Certificados de Qualidade</t>
   </si>
   <si>
-    <t>34726</t>
+    <t>18330872612</t>
   </si>
   <si>
     <t>Inconsistência de saldos entre WMS e ERP na pré-lista WEB</t>
   </si>
   <si>
-    <t>33441</t>
+    <t>18236205584</t>
   </si>
   <si>
     <t>Melhoria de copia de analise e processos</t>
   </si>
   <si>
-    <t>34727</t>
+    <t>18330872575</t>
   </si>
   <si>
     <t>Problema na alocação de materiais no sistema de Pré-Lista Web</t>
   </si>
   <si>
-    <t>34948</t>
+    <t>10549926336</t>
   </si>
   <si>
     <t>Correção | Valor Indice faturamento</t>
   </si>
   <si>
-    <t>33387</t>
+    <t>18330593195</t>
   </si>
   <si>
     <t>HORIMETRO MANIPULADORES</t>
   </si>
   <si>
-    <t>33774</t>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>18302031506</t>
   </si>
   <si>
     <t>Erro - Inventario Finalizado</t>
   </si>
   <si>
-    <t>32037</t>
+    <t>18236204264</t>
   </si>
   <si>
     <t>BI ajustagem</t>
   </si>
   <si>
-    <t>34635</t>
+    <t>18331085190</t>
   </si>
   <si>
     <t>Melhoria B. I. (copy)</t>
   </si>
   <si>
-    <t>35175</t>
+    <t>10557595106</t>
   </si>
   <si>
     <t>Alterações Planilhão Agrupamento de Lotes</t>
   </si>
   <si>
-    <t>13/11/2025</t>
-  </si>
-  <si>
     <t>30069</t>
   </si>
   <si>
@@ -642,7 +672,10 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>33570</t>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>18236206054</t>
   </si>
   <si>
     <t>TEMPOS ZERADOS - MODELOS UPR</t>
@@ -654,7 +687,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-23</t>
+    <t>Out/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1287,13 +1320,13 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1334,7 +1367,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1351,7 +1384,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1363,10 +1396,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1381,7 +1414,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1398,7 +1431,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1410,10 +1443,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1428,13 +1461,13 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1445,37 +1478,37 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1492,7 +1525,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1504,10 +1537,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>35</v>
@@ -1522,13 +1555,13 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1539,7 +1572,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1551,10 +1584,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1569,10 +1602,10 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
@@ -1586,7 +1619,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1598,10 +1631,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1616,7 +1649,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1633,22 +1666,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1663,7 +1696,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1680,7 +1713,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1692,10 +1725,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>35</v>
@@ -1710,13 +1743,13 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -1727,7 +1760,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1739,10 +1772,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1757,7 +1790,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1774,7 +1807,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1786,10 +1819,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>35</v>
@@ -1804,13 +1837,13 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>27</v>
@@ -1821,7 +1854,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1833,10 +1866,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1848,10 +1881,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1868,7 +1901,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1880,10 +1913,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>35</v>
@@ -1898,13 +1931,13 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>27</v>
@@ -1915,22 +1948,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1942,10 +1975,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1954,7 +1987,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1962,7 +1995,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1974,10 +2007,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2009,22 +2042,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2036,10 +2069,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2056,7 +2089,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2068,10 +2101,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>35</v>
@@ -2086,7 +2119,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2103,22 +2136,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2133,7 +2166,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2150,7 +2183,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2162,10 +2195,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>35</v>
@@ -2180,7 +2213,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2197,43 +2230,43 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>27</v>
@@ -2244,7 +2277,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2256,10 +2289,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>35</v>
@@ -2274,7 +2307,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2291,22 +2324,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2321,7 +2354,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2338,22 +2371,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2368,7 +2401,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2385,7 +2418,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2397,10 +2430,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2412,10 +2445,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2424,45 +2457,45 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2471,15 +2504,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2491,10 +2524,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2506,10 +2539,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2518,62 +2551,62 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2585,10 +2618,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2600,10 +2633,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2612,15 +2645,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2632,10 +2665,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>35</v>
@@ -2647,10 +2680,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2659,15 +2692,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2679,10 +2712,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2694,10 +2727,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2706,77 +2739,77 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>35</v>
@@ -2788,27 +2821,27 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2820,10 +2853,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2835,27 +2868,27 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O36" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2867,10 +2900,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>35</v>
@@ -2882,10 +2915,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2894,15 +2927,15 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2914,10 +2947,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2929,10 +2962,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2941,15 +2974,15 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2961,10 +2994,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2976,10 +3009,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2988,15 +3021,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3008,10 +3041,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3023,10 +3056,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -3035,15 +3068,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3055,10 +3088,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3070,10 +3103,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -3082,15 +3115,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3102,10 +3135,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3117,10 +3150,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3129,15 +3162,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3149,10 +3182,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3164,10 +3197,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3176,15 +3209,15 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3196,10 +3229,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3214,10 +3247,10 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3231,7 +3264,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3243,10 +3276,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>35</v>
@@ -3258,27 +3291,27 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3290,10 +3323,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3305,10 +3338,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3317,15 +3350,15 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3337,10 +3370,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3355,7 +3388,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3372,7 +3405,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3384,10 +3417,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3399,10 +3432,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3411,15 +3444,15 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3431,10 +3464,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3446,10 +3479,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3458,15 +3491,15 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3478,10 +3511,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3493,10 +3526,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3505,15 +3538,15 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3525,10 +3558,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3540,27 +3573,27 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O51" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3569,28 +3602,28 @@
         <v>17</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>157</v>
+        <v>31</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3599,15 +3632,15 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3619,10 +3652,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3634,10 +3667,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3646,77 +3679,77 @@
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>35</v>
@@ -3731,7 +3764,7 @@
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3748,7 +3781,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3760,10 +3793,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3775,27 +3808,27 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3807,13 +3840,13 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>21</v>
@@ -3825,7 +3858,7 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3842,7 +3875,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3854,10 +3887,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3872,7 +3905,7 @@
         <v>23</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3889,7 +3922,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3901,10 +3934,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3919,10 +3952,10 @@
         <v>23</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
@@ -3936,7 +3969,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3948,10 +3981,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3963,10 +3996,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -3975,15 +4008,15 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3995,10 +4028,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>35</v>
@@ -4013,7 +4046,7 @@
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4030,37 +4063,37 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4077,7 +4110,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4089,10 +4122,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4104,10 +4137,10 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -4116,15 +4149,15 @@
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4136,10 +4169,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4151,27 +4184,27 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4183,13 +4216,13 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>21</v>
@@ -4201,7 +4234,7 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4218,7 +4251,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4230,10 +4263,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4245,10 +4278,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4257,15 +4290,15 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O66" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4277,13 +4310,13 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>21</v>
@@ -4295,7 +4328,7 @@
         <v>23</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4312,22 +4345,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4339,10 +4372,10 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4351,7 +4384,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
@@ -4359,7 +4392,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4371,10 +4404,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4389,13 +4422,13 @@
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>27</v>
@@ -4406,7 +4439,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4418,10 +4451,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4433,10 +4466,10 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4445,15 +4478,15 @@
         <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4465,10 +4498,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>35</v>
@@ -4480,27 +4513,27 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O71" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O71" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4512,10 +4545,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>35</v>
@@ -4530,7 +4563,7 @@
         <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -4547,7 +4580,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4559,10 +4592,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4574,10 +4607,10 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4586,7 +4619,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
@@ -4594,37 +4627,37 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4633,15 +4666,15 @@
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4653,10 +4686,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4668,10 +4701,10 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4680,10 +4713,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O75" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -4699,23 +4732,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4723,16 +4756,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4743,15 +4776,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>169.25</v>
+        <v>15.57</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4764,7 +4797,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K23">
         <v>7</v>
@@ -4772,7 +4805,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4803,12 +4836,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B2">
         <v>74</v>
@@ -4822,35 +4855,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>169.25</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4858,7 +4891,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4867,13 +4900,13 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4888,18 +4921,18 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -4914,30 +4947,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -4949,53 +4982,59 @@
         <v>54</v>
       </c>
       <c r="J12" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="Q12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="G14" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N14">
         <v>7</v>
@@ -5003,7 +5042,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -5011,7 +5050,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5019,7 +5058,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5027,10 +5066,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5038,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5046,142 +5085,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
